--- a/data7.xlsx
+++ b/data7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myrepos\R-Hyphothesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AADC7FB-9173-47C8-9B4E-9B0211266337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D7F207-9704-44A5-9DF6-5EBA54A2BB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3696" yWindow="2460" windowWidth="8052" windowHeight="8892" xr2:uid="{9319F6A2-DF05-48AC-84AF-7300389DD8A5}"/>
   </bookViews>
@@ -428,457 +428,457 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1200</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>3000</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>3500</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>3500</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>3500</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>4499</v>
+        <v>4001</v>
       </c>
     </row>
   </sheetData>
